--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Revelation_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Revelation_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R1c3f4ecb1a184692"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R87b2c89318ac491b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Re2fa4d011eb74b0d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R0bdc0e06e72f4d22"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="Re6d452ca7ccc4c30"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="Rae1ee660d7a74074"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R75dfe2568bdb4538"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="Re9ad04f3a707455b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Rdfd9132f49de4017"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="Rf64ff9184780480e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R134370357faf40ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="Raa9bd4ba1f794943"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R39b794bef0cb42aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R13be7d11ee824ba1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R1902bdfb7e504743"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R2a4e86bf6c514487"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R085959ae8cfd4094"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R2354bf324bd34280"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R81a94d47e82b483b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R4949eb815ff046bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="Rbce4a805175248ed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R02fd294421e74e70"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="Rf5be55b8fff941f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R02a2cfdd4af54b45"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R23b231e420d440c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R02cf55e2b5fb4d52"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R9c6b1c7ccbfb4008"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R48cb4740f2d44f27"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rbadfbf77a83943eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="Rd5121f97b7a84763"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R27bf38292c0c463a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R977e0bc9020d40ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R41028a70b71349f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R180a60fe720f425d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R7276565e08c94737"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R38873c10765e4ae4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R19f62fb58f7d4a95"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R49f60ec43bbb4fda"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R3d5a9165ee8a40ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R39bce930b1bb436c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R18f8e5f2ecbc40f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="Rad11ce2c56fb47cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R94451aecdf1144df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R1930d91796a44962"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R418f12c803ac47d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="Re1a817d956964f73"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R7031cc52b2fe4fc8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="Re42b3561b0184911"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R0b3319192583403d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R59d78e450dfa4531"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R424b76f9f0fe421c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R6fc0ed0d59a8434a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R9c2c05c7f7114fe2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R055d01008ebf4792"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R2808e5ffe5e44dda"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="Rc21d5227470e4314"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -174,7 +174,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="45">
+  <x:cellXfs count="43">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -230,12 +230,6 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
@@ -2156,7 +2150,7 @@
       <x:c r="A5" s="2" t="str">
         <x:v>Fiches suivies</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:f>SUM(B10:B35)</x:f>
         <x:v>158</x:v>
       </x:c>
@@ -2164,7 +2158,7 @@
       <x:c r="D5" s="2" t="str">
         <x:v>Intégrés</x:v>
       </x:c>
-      <x:c r="E5" s="33" t="n">
+      <x:c r="E5" s="31" t="n">
         <x:f>SUM(E10:F35)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2172,7 +2166,7 @@
       <x:c r="G5" s="2" t="str">
         <x:v>À vérifier</x:v>
       </x:c>
-      <x:c r="H5" s="33" t="n">
+      <x:c r="H5" s="31" t="n">
         <x:f>SUM(H10:H35)</x:f>
         <x:v>1</x:v>
       </x:c>
@@ -2180,7 +2174,7 @@
       <x:c r="J5" s="2" t="str">
         <x:v>Extrapolations</x:v>
       </x:c>
-      <x:c r="K5" s="33" t="n">
+      <x:c r="K5" s="31" t="n">
         <x:f>SUM(I10:I35)</x:f>
         <x:v>132</x:v>
       </x:c>
@@ -2203,7 +2197,7 @@
       <x:c r="M6" s="2"/>
     </x:row>
     <x:row r="7" ht="22" customHeight="1">
-      <x:c r="A7" s="34" t="str">
+      <x:c r="A7" s="32" t="str">
         <x:v>Défini = spécification. Établi = référence documentée. Les colonnes d’adaptation restent des propositions.</x:v>
       </x:c>
       <x:c r="B7" s="2"/>
@@ -2235,95 +2229,95 @@
       <x:c r="M8" s="2"/>
     </x:row>
     <x:row r="9" ht="34" customHeight="1">
-      <x:c r="A9" s="30" t="str">
+      <x:c r="A9" s="28" t="str">
         <x:v>Domaine</x:v>
       </x:c>
-      <x:c r="B9" s="31" t="str">
+      <x:c r="B9" s="29" t="str">
         <x:v>Total</x:v>
       </x:c>
-      <x:c r="C9" s="31" t="str">
+      <x:c r="C9" s="29" t="str">
         <x:v>Défini</x:v>
       </x:c>
-      <x:c r="D9" s="31" t="str">
+      <x:c r="D9" s="29" t="str">
         <x:v>Prototype</x:v>
       </x:c>
-      <x:c r="E9" s="31" t="str">
+      <x:c r="E9" s="29" t="str">
         <x:v>Intégré</x:v>
       </x:c>
-      <x:c r="F9" s="31" t="str">
+      <x:c r="F9" s="29" t="str">
         <x:v>Validé</x:v>
       </x:c>
-      <x:c r="G9" s="31" t="str">
+      <x:c r="G9" s="29" t="str">
         <x:v>Établi</x:v>
       </x:c>
-      <x:c r="H9" s="31" t="str">
+      <x:c r="H9" s="29" t="str">
         <x:v>À vérifier</x:v>
       </x:c>
-      <x:c r="I9" s="31" t="str">
+      <x:c r="I9" s="29" t="str">
         <x:v>Extrapolation</x:v>
       </x:c>
-      <x:c r="J9" s="31" t="str">
+      <x:c r="J9" s="29" t="str">
         <x:v>Coupé attesté</x:v>
       </x:c>
-      <x:c r="K9" s="31" t="str">
+      <x:c r="K9" s="29" t="str">
         <x:v>Concept abandonné</x:v>
       </x:c>
-      <x:c r="L9" s="31" t="str">
+      <x:c r="L9" s="29" t="str">
         <x:v>Allégation écartée</x:v>
       </x:c>
-      <x:c r="M9" s="32" t="str">
+      <x:c r="M9" s="30" t="str">
         <x:v>Priorité P0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="22" customHeight="1">
-      <x:c r="A10" s="35" t="str">
+      <x:c r="A10" s="33" t="str">
         <x:v>Personnages</x:v>
       </x:c>
-      <x:c r="B10" s="39" t="n">
+      <x:c r="B10" s="37" t="n">
         <x:f>COUNTA('Personnages'!$A$7:$A$9)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C10" s="39" t="n">
+      <x:c r="C10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$9,"Défini")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D10" s="39" t="n">
+      <x:c r="D10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$9,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E10" s="39" t="n">
+      <x:c r="E10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$9,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F10" s="39" t="n">
+      <x:c r="F10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$9,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G10" s="39" t="n">
+      <x:c r="G10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$9,"Établi")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H10" s="39" t="n">
+      <x:c r="H10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$9,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I10" s="39" t="n">
+      <x:c r="I10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$9,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J10" s="39" t="n">
+      <x:c r="J10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$9,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K10" s="39" t="n">
+      <x:c r="K10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$9,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L10" s="39" t="n">
+      <x:c r="L10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$9,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M10" s="39" t="n">
+      <x:c r="M10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$E$7:$E$9,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2332,104 +2326,104 @@
       <x:c r="A11" s="2" t="str">
         <x:v>PNJ</x:v>
       </x:c>
-      <x:c r="B11" s="40" t="n">
+      <x:c r="B11" s="38" t="n">
         <x:f>COUNTA('PNJ'!$A$7:$A$13)</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C11" s="40" t="n">
+      <x:c r="C11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$13,"Défini")</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D11" s="40" t="n">
+      <x:c r="D11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$13,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E11" s="40" t="n">
+      <x:c r="E11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$13,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F11" s="40" t="n">
+      <x:c r="F11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$13,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G11" s="40" t="n">
+      <x:c r="G11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$13,"Établi")</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H11" s="40" t="n">
+      <x:c r="H11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$13,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I11" s="40" t="n">
+      <x:c r="I11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$13,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J11" s="40" t="n">
+      <x:c r="J11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$13,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K11" s="40" t="n">
+      <x:c r="K11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$13,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L11" s="40" t="n">
+      <x:c r="L11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$13,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M11" s="40" t="n">
+      <x:c r="M11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$E$7:$E$13,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="22" customHeight="1">
-      <x:c r="A12" s="35" t="str">
+      <x:c r="A12" s="33" t="str">
         <x:v>Espèces et factions</x:v>
       </x:c>
-      <x:c r="B12" s="39" t="n">
+      <x:c r="B12" s="37" t="n">
         <x:f>COUNTA('Especes_factions'!$A$7:$A$9)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C12" s="39" t="n">
+      <x:c r="C12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$9,"Défini")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D12" s="37" t="n">
+        <x:f>COUNTIFS('Especes_factions'!$C$7:$C$9,"Prototype")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D12" s="39" t="n">
-        <x:f>COUNTIFS('Especes_factions'!$C$7:$C$9,"Prototype")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E12" s="39" t="n">
+      <x:c r="E12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$9,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F12" s="39" t="n">
+      <x:c r="F12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$9,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G12" s="39" t="n">
+      <x:c r="G12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$9,"Établi")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H12" s="39" t="n">
+      <x:c r="H12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$9,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I12" s="39" t="n">
+      <x:c r="I12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$9,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J12" s="39" t="n">
+      <x:c r="J12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$9,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K12" s="39" t="n">
+      <x:c r="K12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$9,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L12" s="39" t="n">
+      <x:c r="L12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$9,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M12" s="39" t="n">
+      <x:c r="M12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$E$7:$E$9,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2438,104 +2432,104 @@
       <x:c r="A13" s="2" t="str">
         <x:v>Mondes</x:v>
       </x:c>
-      <x:c r="B13" s="40" t="n">
+      <x:c r="B13" s="38" t="n">
         <x:f>COUNTA('Mondes'!$A$7:$A$10)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C13" s="40" t="n">
+      <x:c r="C13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$10,"Défini")</x:f>
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D13" s="40" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$10,"Prototype")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E13" s="40" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$10,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F13" s="40" t="n">
+      <x:c r="F13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$10,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G13" s="40" t="n">
+      <x:c r="G13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$10,"Établi")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="H13" s="40" t="n">
+      <x:c r="H13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$10,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I13" s="40" t="n">
+      <x:c r="I13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$10,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J13" s="40" t="n">
+      <x:c r="J13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$10,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K13" s="40" t="n">
+      <x:c r="K13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$10,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L13" s="40" t="n">
+      <x:c r="L13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$10,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M13" s="40" t="n">
+      <x:c r="M13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$E$7:$E$10,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="22" customHeight="1">
-      <x:c r="A14" s="35" t="str">
+      <x:c r="A14" s="33" t="str">
         <x:v>Zones</x:v>
       </x:c>
-      <x:c r="B14" s="39" t="n">
+      <x:c r="B14" s="37" t="n">
         <x:f>COUNTA('Zones'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C14" s="39" t="n">
+      <x:c r="C14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D14" s="39" t="n">
+      <x:c r="D14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E14" s="39" t="n">
+      <x:c r="E14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F14" s="39" t="n">
+      <x:c r="F14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G14" s="39" t="n">
+      <x:c r="G14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H14" s="39" t="n">
+      <x:c r="H14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I14" s="39" t="n">
+      <x:c r="I14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J14" s="39" t="n">
+      <x:c r="J14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K14" s="39" t="n">
+      <x:c r="K14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L14" s="39" t="n">
+      <x:c r="L14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M14" s="39" t="n">
+      <x:c r="M14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2544,104 +2538,104 @@
       <x:c r="A15" s="2" t="str">
         <x:v>Liaisons</x:v>
       </x:c>
-      <x:c r="B15" s="40" t="n">
+      <x:c r="B15" s="38" t="n">
         <x:f>COUNTA('Liaisons'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C15" s="40" t="n">
+      <x:c r="C15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D15" s="40" t="n">
+      <x:c r="D15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E15" s="40" t="n">
+      <x:c r="E15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F15" s="40" t="n">
+      <x:c r="F15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G15" s="40" t="n">
+      <x:c r="G15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H15" s="40" t="n">
+      <x:c r="H15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I15" s="40" t="n">
+      <x:c r="I15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J15" s="40" t="n">
+      <x:c r="J15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K15" s="40" t="n">
+      <x:c r="K15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L15" s="40" t="n">
+      <x:c r="L15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M15" s="40" t="n">
+      <x:c r="M15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="22" customHeight="1">
-      <x:c r="A16" s="35" t="str">
+      <x:c r="A16" s="33" t="str">
         <x:v>Décors</x:v>
       </x:c>
-      <x:c r="B16" s="39" t="n">
+      <x:c r="B16" s="37" t="n">
         <x:f>COUNTA('Decors'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C16" s="39" t="n">
+      <x:c r="C16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D16" s="39" t="n">
+      <x:c r="D16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E16" s="39" t="n">
+      <x:c r="E16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F16" s="39" t="n">
+      <x:c r="F16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G16" s="39" t="n">
+      <x:c r="G16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H16" s="39" t="n">
+      <x:c r="H16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I16" s="39" t="n">
+      <x:c r="I16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J16" s="39" t="n">
+      <x:c r="J16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K16" s="39" t="n">
+      <x:c r="K16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L16" s="39" t="n">
+      <x:c r="L16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M16" s="39" t="n">
+      <x:c r="M16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2650,104 +2644,104 @@
       <x:c r="A17" s="2" t="str">
         <x:v>Props</x:v>
       </x:c>
-      <x:c r="B17" s="40" t="n">
+      <x:c r="B17" s="38" t="n">
         <x:f>COUNTA('Props'!$A$7:$A$7)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C17" s="40" t="n">
+      <x:c r="C17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$7,"Défini")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D17" s="40" t="n">
+      <x:c r="D17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$7,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E17" s="40" t="n">
+      <x:c r="E17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$7,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F17" s="40" t="n">
+      <x:c r="F17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$7,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G17" s="40" t="n">
+      <x:c r="G17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$7,"Établi")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H17" s="40" t="n">
+      <x:c r="H17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$7,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I17" s="40" t="n">
+      <x:c r="I17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$7,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J17" s="40" t="n">
+      <x:c r="J17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$7,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K17" s="40" t="n">
+      <x:c r="K17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$7,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L17" s="40" t="n">
+      <x:c r="L17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$7,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M17" s="40" t="n">
+      <x:c r="M17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$E$7:$E$7,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="22" customHeight="1">
-      <x:c r="A18" s="35" t="str">
+      <x:c r="A18" s="33" t="str">
         <x:v>Ennemis et boss</x:v>
       </x:c>
-      <x:c r="B18" s="39" t="n">
+      <x:c r="B18" s="37" t="n">
         <x:f>COUNTA('Ennemis_boss'!$A$7:$A$10)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C18" s="39" t="n">
+      <x:c r="C18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$10,"Défini")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D18" s="39" t="n">
+      <x:c r="D18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$10,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E18" s="39" t="n">
+      <x:c r="E18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$10,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F18" s="39" t="n">
+      <x:c r="F18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$10,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G18" s="39" t="n">
+      <x:c r="G18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H18" s="39" t="n">
+      <x:c r="H18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I18" s="39" t="n">
+      <x:c r="I18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"Extrapolation")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="J18" s="39" t="n">
+      <x:c r="J18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K18" s="39" t="n">
+      <x:c r="K18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L18" s="39" t="n">
+      <x:c r="L18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M18" s="39" t="n">
+      <x:c r="M18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$E$7:$E$10,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2756,104 +2750,104 @@
       <x:c r="A19" s="2" t="str">
         <x:v>Missions</x:v>
       </x:c>
-      <x:c r="B19" s="40" t="n">
+      <x:c r="B19" s="38" t="n">
         <x:f>COUNTA('Missions'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C19" s="40" t="n">
+      <x:c r="C19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D19" s="40" t="n">
+      <x:c r="D19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E19" s="40" t="n">
+      <x:c r="E19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F19" s="40" t="n">
+      <x:c r="F19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G19" s="40" t="n">
+      <x:c r="G19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H19" s="40" t="n">
+      <x:c r="H19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I19" s="40" t="n">
+      <x:c r="I19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J19" s="40" t="n">
+      <x:c r="J19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K19" s="40" t="n">
+      <x:c r="K19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L19" s="40" t="n">
+      <x:c r="L19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M19" s="40" t="n">
+      <x:c r="M19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$E$7:$E$14,"P0")</x:f>
         <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="22" customHeight="1">
-      <x:c r="A20" s="35" t="str">
+      <x:c r="A20" s="33" t="str">
         <x:v>Secondaires et DLC</x:v>
       </x:c>
-      <x:c r="B20" s="39" t="n">
+      <x:c r="B20" s="37" t="n">
         <x:f>COUNTA('Secondaires_DLC'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C20" s="39" t="n">
+      <x:c r="C20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D20" s="39" t="n">
+      <x:c r="D20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E20" s="39" t="n">
+      <x:c r="E20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F20" s="39" t="n">
+      <x:c r="F20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G20" s="39" t="n">
+      <x:c r="G20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H20" s="39" t="n">
+      <x:c r="H20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I20" s="39" t="n">
+      <x:c r="I20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J20" s="39" t="n">
+      <x:c r="J20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K20" s="39" t="n">
+      <x:c r="K20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L20" s="39" t="n">
+      <x:c r="L20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M20" s="39" t="n">
+      <x:c r="M20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2862,104 +2856,104 @@
       <x:c r="A21" s="2" t="str">
         <x:v>Choix et relations</x:v>
       </x:c>
-      <x:c r="B21" s="40" t="n">
+      <x:c r="B21" s="38" t="n">
         <x:f>COUNTA('Choix_relations'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C21" s="40" t="n">
+      <x:c r="C21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D21" s="40" t="n">
+      <x:c r="D21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E21" s="40" t="n">
+      <x:c r="E21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F21" s="40" t="n">
+      <x:c r="F21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G21" s="40" t="n">
+      <x:c r="G21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H21" s="40" t="n">
+      <x:c r="H21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I21" s="40" t="n">
+      <x:c r="I21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J21" s="40" t="n">
+      <x:c r="J21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K21" s="40" t="n">
+      <x:c r="K21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L21" s="40" t="n">
+      <x:c r="L21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M21" s="40" t="n">
+      <x:c r="M21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="22" customHeight="1">
-      <x:c r="A22" s="35" t="str">
+      <x:c r="A22" s="33" t="str">
         <x:v>Dialogues</x:v>
       </x:c>
-      <x:c r="B22" s="39" t="n">
+      <x:c r="B22" s="37" t="n">
         <x:f>COUNTA('Dialogues'!$A$7:$A$16)</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C22" s="39" t="n">
+      <x:c r="C22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$16,"Défini")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D22" s="39" t="n">
+      <x:c r="D22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$16,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E22" s="39" t="n">
+      <x:c r="E22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$16,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F22" s="39" t="n">
+      <x:c r="F22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$16,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G22" s="39" t="n">
+      <x:c r="G22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$16,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H22" s="39" t="n">
+      <x:c r="H22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$16,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I22" s="39" t="n">
+      <x:c r="I22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$16,"Extrapolation")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J22" s="39" t="n">
+      <x:c r="J22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$16,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K22" s="39" t="n">
+      <x:c r="K22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$16,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L22" s="39" t="n">
+      <x:c r="L22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$16,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M22" s="39" t="n">
+      <x:c r="M22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$E$7:$E$16,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2968,104 +2962,104 @@
       <x:c r="A23" s="2" t="str">
         <x:v>Cinématiques</x:v>
       </x:c>
-      <x:c r="B23" s="40" t="n">
+      <x:c r="B23" s="38" t="n">
         <x:f>COUNTA('Cinematiques'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C23" s="40" t="n">
+      <x:c r="C23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D23" s="40" t="n">
+      <x:c r="D23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E23" s="40" t="n">
+      <x:c r="E23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F23" s="40" t="n">
+      <x:c r="F23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G23" s="40" t="n">
+      <x:c r="G23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H23" s="40" t="n">
+      <x:c r="H23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I23" s="40" t="n">
+      <x:c r="I23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J23" s="40" t="n">
+      <x:c r="J23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K23" s="40" t="n">
+      <x:c r="K23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L23" s="40" t="n">
+      <x:c r="L23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M23" s="40" t="n">
+      <x:c r="M23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="22" customHeight="1">
-      <x:c r="A24" s="35" t="str">
+      <x:c r="A24" s="33" t="str">
         <x:v>Armes</x:v>
       </x:c>
-      <x:c r="B24" s="39" t="n">
+      <x:c r="B24" s="37" t="n">
         <x:f>COUNTA('Armes'!$A$7:$A$7)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C24" s="39" t="n">
+      <x:c r="C24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$7,"Défini")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D24" s="39" t="n">
+      <x:c r="D24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$7,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E24" s="39" t="n">
+      <x:c r="E24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$7,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F24" s="39" t="n">
+      <x:c r="F24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$7,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G24" s="39" t="n">
+      <x:c r="G24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Établi")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H24" s="39" t="n">
+      <x:c r="H24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I24" s="39" t="n">
+      <x:c r="I24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J24" s="39" t="n">
+      <x:c r="J24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K24" s="39" t="n">
+      <x:c r="K24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L24" s="39" t="n">
+      <x:c r="L24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M24" s="39" t="n">
+      <x:c r="M24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$E$7:$E$7,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3074,104 +3068,104 @@
       <x:c r="A25" s="2" t="str">
         <x:v>Armures et équipement</x:v>
       </x:c>
-      <x:c r="B25" s="40" t="n">
+      <x:c r="B25" s="38" t="n">
         <x:f>COUNTA('Armures_equipement'!$A$7:$A$8)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C25" s="40" t="n">
+      <x:c r="C25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$8,"Défini")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D25" s="40" t="n">
+      <x:c r="D25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$8,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E25" s="40" t="n">
+      <x:c r="E25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$8,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F25" s="40" t="n">
+      <x:c r="F25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$8,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G25" s="40" t="n">
+      <x:c r="G25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$8,"Établi")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H25" s="40" t="n">
+      <x:c r="H25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$8,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I25" s="40" t="n">
+      <x:c r="I25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$8,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J25" s="40" t="n">
+      <x:c r="J25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$8,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K25" s="40" t="n">
+      <x:c r="K25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$8,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L25" s="40" t="n">
+      <x:c r="L25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$8,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M25" s="40" t="n">
+      <x:c r="M25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$E$7:$E$8,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="22" customHeight="1">
-      <x:c r="A26" s="35" t="str">
+      <x:c r="A26" s="33" t="str">
         <x:v>Pouvoirs</x:v>
       </x:c>
-      <x:c r="B26" s="39" t="n">
+      <x:c r="B26" s="37" t="n">
         <x:f>COUNTA('Pouvoirs'!$A$7:$A$7)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C26" s="39" t="n">
+      <x:c r="C26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$7,"Défini")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D26" s="39" t="n">
+      <x:c r="D26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$7,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E26" s="39" t="n">
+      <x:c r="E26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$7,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F26" s="39" t="n">
+      <x:c r="F26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$7,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G26" s="39" t="n">
+      <x:c r="G26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Établi")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H26" s="39" t="n">
+      <x:c r="H26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I26" s="39" t="n">
+      <x:c r="I26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J26" s="39" t="n">
+      <x:c r="J26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K26" s="39" t="n">
+      <x:c r="K26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L26" s="39" t="n">
+      <x:c r="L26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M26" s="39" t="n">
+      <x:c r="M26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$E$7:$E$7,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3180,104 +3174,104 @@
       <x:c r="A27" s="2" t="str">
         <x:v>Movesets alliés</x:v>
       </x:c>
-      <x:c r="B27" s="40" t="n">
+      <x:c r="B27" s="38" t="n">
         <x:f>COUNTA('Movesets_allies'!$A$7:$A$12)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C27" s="40" t="n">
+      <x:c r="C27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$12,"Défini")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D27" s="40" t="n">
+      <x:c r="D27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$12,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E27" s="40" t="n">
+      <x:c r="E27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$12,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F27" s="40" t="n">
+      <x:c r="F27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$12,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G27" s="40" t="n">
+      <x:c r="G27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$12,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H27" s="40" t="n">
+      <x:c r="H27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$12,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I27" s="40" t="n">
+      <x:c r="I27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$12,"Extrapolation")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="J27" s="40" t="n">
+      <x:c r="J27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$12,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K27" s="40" t="n">
+      <x:c r="K27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$12,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L27" s="40" t="n">
+      <x:c r="L27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$12,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M27" s="40" t="n">
+      <x:c r="M27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$E$7:$E$12,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="22" customHeight="1">
-      <x:c r="A28" s="35" t="str">
+      <x:c r="A28" s="33" t="str">
         <x:v>Movesets ennemis</x:v>
       </x:c>
-      <x:c r="B28" s="39" t="n">
+      <x:c r="B28" s="37" t="n">
         <x:f>COUNTA('Movesets_ennemis'!$A$7:$A$10)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C28" s="39" t="n">
+      <x:c r="C28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$10,"Défini")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D28" s="39" t="n">
+      <x:c r="D28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$10,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E28" s="39" t="n">
+      <x:c r="E28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$10,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F28" s="39" t="n">
+      <x:c r="F28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$10,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G28" s="39" t="n">
+      <x:c r="G28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$10,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H28" s="39" t="n">
+      <x:c r="H28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$10,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I28" s="39" t="n">
+      <x:c r="I28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$10,"Extrapolation")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="J28" s="39" t="n">
+      <x:c r="J28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$10,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K28" s="39" t="n">
+      <x:c r="K28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$10,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L28" s="39" t="n">
+      <x:c r="L28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$10,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M28" s="39" t="n">
+      <x:c r="M28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$E$7:$E$10,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3286,104 +3280,104 @@
       <x:c r="A29" s="2" t="str">
         <x:v>Animations</x:v>
       </x:c>
-      <x:c r="B29" s="40" t="n">
+      <x:c r="B29" s="38" t="n">
         <x:f>COUNTA('Animations'!$A$7:$A$16)</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C29" s="40" t="n">
+      <x:c r="C29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$16,"Défini")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D29" s="40" t="n">
+      <x:c r="D29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$16,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E29" s="40" t="n">
+      <x:c r="E29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$16,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F29" s="40" t="n">
+      <x:c r="F29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$16,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G29" s="40" t="n">
+      <x:c r="G29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$16,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H29" s="40" t="n">
+      <x:c r="H29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$16,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I29" s="40" t="n">
+      <x:c r="I29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$16,"Extrapolation")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J29" s="40" t="n">
+      <x:c r="J29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$16,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K29" s="40" t="n">
+      <x:c r="K29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$16,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L29" s="40" t="n">
+      <x:c r="L29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$16,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M29" s="40" t="n">
+      <x:c r="M29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$E$7:$E$16,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="22" customHeight="1">
-      <x:c r="A30" s="35" t="str">
+      <x:c r="A30" s="33" t="str">
         <x:v>Sprites</x:v>
       </x:c>
-      <x:c r="B30" s="39" t="n">
+      <x:c r="B30" s="37" t="n">
         <x:f>COUNTA('Sprites'!$A$7:$A$16)</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C30" s="39" t="n">
+      <x:c r="C30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$16,"Défini")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D30" s="39" t="n">
+      <x:c r="D30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$16,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E30" s="39" t="n">
+      <x:c r="E30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$16,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F30" s="39" t="n">
+      <x:c r="F30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$16,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G30" s="39" t="n">
+      <x:c r="G30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$16,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H30" s="39" t="n">
+      <x:c r="H30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$16,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I30" s="39" t="n">
+      <x:c r="I30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$16,"Extrapolation")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J30" s="39" t="n">
+      <x:c r="J30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$16,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K30" s="39" t="n">
+      <x:c r="K30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$16,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L30" s="39" t="n">
+      <x:c r="L30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$16,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M30" s="39" t="n">
+      <x:c r="M30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$E$7:$E$16,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3392,104 +3386,104 @@
       <x:c r="A31" s="2" t="str">
         <x:v>VFX</x:v>
       </x:c>
-      <x:c r="B31" s="40" t="n">
+      <x:c r="B31" s="38" t="n">
         <x:f>COUNTA('VFX'!$A$7:$A$10)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C31" s="40" t="n">
+      <x:c r="C31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$10,"Défini")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D31" s="40" t="n">
+      <x:c r="D31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$10,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E31" s="40" t="n">
+      <x:c r="E31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$10,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F31" s="40" t="n">
+      <x:c r="F31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$10,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G31" s="40" t="n">
+      <x:c r="G31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$10,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H31" s="40" t="n">
+      <x:c r="H31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$10,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I31" s="40" t="n">
+      <x:c r="I31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$10,"Extrapolation")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="J31" s="40" t="n">
+      <x:c r="J31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$10,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K31" s="40" t="n">
+      <x:c r="K31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$10,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L31" s="40" t="n">
+      <x:c r="L31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$10,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M31" s="40" t="n">
+      <x:c r="M31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$E$7:$E$10,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="22" customHeight="1">
-      <x:c r="A32" s="35" t="str">
+      <x:c r="A32" s="33" t="str">
         <x:v>Audio</x:v>
       </x:c>
-      <x:c r="B32" s="39" t="n">
+      <x:c r="B32" s="37" t="n">
         <x:f>COUNTA('Audio'!$A$7:$A$11)</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C32" s="39" t="n">
+      <x:c r="C32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$11,"Défini")</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D32" s="39" t="n">
+      <x:c r="D32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$11,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E32" s="39" t="n">
+      <x:c r="E32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$11,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F32" s="39" t="n">
+      <x:c r="F32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$11,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G32" s="39" t="n">
+      <x:c r="G32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$11,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H32" s="39" t="n">
+      <x:c r="H32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$11,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I32" s="39" t="n">
+      <x:c r="I32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$11,"Extrapolation")</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="J32" s="39" t="n">
+      <x:c r="J32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$11,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K32" s="39" t="n">
+      <x:c r="K32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$11,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L32" s="39" t="n">
+      <x:c r="L32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$11,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M32" s="39" t="n">
+      <x:c r="M32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$E$7:$E$11,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3498,104 +3492,104 @@
       <x:c r="A33" s="2" t="str">
         <x:v>Systèmes et UI</x:v>
       </x:c>
-      <x:c r="B33" s="40" t="n">
+      <x:c r="B33" s="38" t="n">
         <x:f>COUNTA('UI_systemes'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C33" s="40" t="n">
+      <x:c r="C33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D33" s="40" t="n">
+      <x:c r="D33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E33" s="40" t="n">
+      <x:c r="E33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F33" s="40" t="n">
+      <x:c r="F33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G33" s="40" t="n">
+      <x:c r="G33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H33" s="40" t="n">
+      <x:c r="H33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I33" s="40" t="n">
+      <x:c r="I33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J33" s="40" t="n">
+      <x:c r="J33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K33" s="40" t="n">
+      <x:c r="K33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L33" s="40" t="n">
+      <x:c r="L33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M33" s="40" t="n">
+      <x:c r="M33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$E$7:$E$14,"P0")</x:f>
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="22" customHeight="1">
-      <x:c r="A34" s="35" t="str">
+      <x:c r="A34" s="33" t="str">
         <x:v>QA</x:v>
       </x:c>
-      <x:c r="B34" s="39" t="n">
+      <x:c r="B34" s="37" t="n">
         <x:f>COUNTA('QA'!$A$7:$A$18)</x:f>
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C34" s="39" t="n">
+      <x:c r="C34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$18,"Défini")</x:f>
         <x:v>12</x:v>
       </x:c>
-      <x:c r="D34" s="39" t="n">
+      <x:c r="D34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$18,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E34" s="39" t="n">
+      <x:c r="E34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$18,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F34" s="39" t="n">
+      <x:c r="F34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$18,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G34" s="39" t="n">
+      <x:c r="G34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$18,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H34" s="39" t="n">
+      <x:c r="H34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$18,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I34" s="39" t="n">
+      <x:c r="I34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$18,"Extrapolation")</x:f>
         <x:v>12</x:v>
       </x:c>
-      <x:c r="J34" s="39" t="n">
+      <x:c r="J34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$18,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K34" s="39" t="n">
+      <x:c r="K34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$18,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L34" s="39" t="n">
+      <x:c r="L34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$18,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M34" s="39" t="n">
+      <x:c r="M34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$E$7:$E$18,"P0")</x:f>
         <x:v>3</x:v>
       </x:c>
@@ -3604,119 +3598,119 @@
       <x:c r="A35" s="2" t="str">
         <x:v>Continuité</x:v>
       </x:c>
-      <x:c r="B35" s="40" t="n">
+      <x:c r="B35" s="38" t="n">
         <x:f>COUNTA('Continuite'!$A$7:$A$13)</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C35" s="40" t="n">
+      <x:c r="C35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$13,"Défini")</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D35" s="40" t="n">
+      <x:c r="D35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$13,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E35" s="40" t="n">
+      <x:c r="E35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$13,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F35" s="40" t="n">
+      <x:c r="F35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$13,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G35" s="40" t="n">
+      <x:c r="G35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$13,"Établi")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H35" s="40" t="n">
+      <x:c r="H35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$13,"À vérifier")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I35" s="40" t="n">
+      <x:c r="I35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$13,"Extrapolation")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="J35" s="40" t="n">
+      <x:c r="J35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$13,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K35" s="40" t="n">
+      <x:c r="K35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$13,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L35" s="40" t="n">
+      <x:c r="L35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$13,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M35" s="40" t="n">
+      <x:c r="M35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$E$7:$E$13,"P0")</x:f>
         <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="22" customHeight="1">
       <x:c r="A36" s="2"/>
-      <x:c r="B36" s="40"/>
-      <x:c r="C36" s="40"/>
-      <x:c r="D36" s="40"/>
-      <x:c r="E36" s="40"/>
-      <x:c r="F36" s="40"/>
-      <x:c r="G36" s="40"/>
-      <x:c r="H36" s="40"/>
-      <x:c r="I36" s="40"/>
-      <x:c r="J36" s="40"/>
-      <x:c r="K36" s="40"/>
-      <x:c r="L36" s="40"/>
-      <x:c r="M36" s="40"/>
+      <x:c r="B36" s="38"/>
+      <x:c r="C36" s="38"/>
+      <x:c r="D36" s="38"/>
+      <x:c r="E36" s="38"/>
+      <x:c r="F36" s="38"/>
+      <x:c r="G36" s="38"/>
+      <x:c r="H36" s="38"/>
+      <x:c r="I36" s="38"/>
+      <x:c r="J36" s="38"/>
+      <x:c r="K36" s="38"/>
+      <x:c r="L36" s="38"/>
+      <x:c r="M36" s="38"/>
     </x:row>
     <x:row r="37" ht="28" customHeight="1">
-      <x:c r="A37" s="23" t="str">
+      <x:c r="A37" s="21" t="str">
         <x:v>TOTAL</x:v>
       </x:c>
-      <x:c r="B37" s="41" t="n">
+      <x:c r="B37" s="39" t="n">
         <x:f>SUM(B10:B35)</x:f>
         <x:v>158</x:v>
       </x:c>
-      <x:c r="C37" s="41" t="n">
+      <x:c r="C37" s="39" t="n">
         <x:f>SUM(C10:C35)</x:f>
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="D37" s="41" t="n">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="D37" s="39" t="n">
         <x:f>SUM(D10:D35)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E37" s="41" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E37" s="39" t="n">
         <x:f>SUM(E10:E35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F37" s="41" t="n">
+      <x:c r="F37" s="39" t="n">
         <x:f>SUM(F10:F35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G37" s="41" t="n">
+      <x:c r="G37" s="39" t="n">
         <x:f>SUM(G10:G35)</x:f>
         <x:v>25</x:v>
       </x:c>
-      <x:c r="H37" s="41" t="n">
+      <x:c r="H37" s="39" t="n">
         <x:f>SUM(H10:H35)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I37" s="41" t="n">
+      <x:c r="I37" s="39" t="n">
         <x:f>SUM(I10:I35)</x:f>
         <x:v>132</x:v>
       </x:c>
-      <x:c r="J37" s="41" t="n">
+      <x:c r="J37" s="39" t="n">
         <x:f>SUM(J10:J35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K37" s="41" t="n">
+      <x:c r="K37" s="39" t="n">
         <x:f>SUM(K10:K35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L37" s="41" t="n">
+      <x:c r="L37" s="39" t="n">
         <x:f>SUM(L10:L35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M37" s="41" t="n">
+      <x:c r="M37" s="39" t="n">
         <x:f>SUM(M10:M35)</x:f>
         <x:v>20</x:v>
       </x:c>
@@ -3940,61 +3934,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -4044,8 +4038,8 @@
       <x:c r="O7" s="9" t="str"/>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str">
         <x:v>Tous comportements et réglages de combat sont du design original.</x:v>
       </x:c>
     </x:row>
@@ -4095,8 +4089,8 @@
       <x:c r="O8" s="7" t="str"/>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str">
         <x:v>Tous comportements et réglages de combat sont du design original.</x:v>
       </x:c>
     </x:row>
@@ -4146,8 +4140,8 @@
       <x:c r="O9" s="9" t="str"/>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str">
         <x:v>Tous comportements et réglages de combat sont du design original.</x:v>
       </x:c>
     </x:row>
@@ -4197,8 +4191,8 @@
       <x:c r="O10" s="7" t="str"/>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str">
         <x:v>Tous comportements et réglages de combat sont du design original.</x:v>
       </x:c>
     </x:row>
@@ -4234,7 +4228,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R568283da7d064848"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R22dfc1a385e249b2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4374,61 +4368,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -4480,8 +4474,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -4531,8 +4525,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -4582,8 +4576,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -4633,8 +4627,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -4684,8 +4678,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -4735,8 +4729,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="68" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -4786,8 +4780,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="68" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -4837,8 +4831,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -4872,7 +4866,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R759ac45c86c041d4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R84ef90daef3847b1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5012,61 +5006,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -5118,8 +5112,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -5169,8 +5163,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -5220,8 +5214,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -5271,8 +5265,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -5322,8 +5316,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -5373,8 +5367,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -5424,8 +5418,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -5475,8 +5469,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -5510,7 +5504,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R840b6bde9e604ac3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d923c4831ac47fd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5650,61 +5644,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -5756,8 +5750,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -5807,8 +5801,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -5858,8 +5852,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -5909,8 +5903,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -5960,8 +5954,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -6011,8 +6005,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -6062,8 +6056,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -6113,8 +6107,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -6148,7 +6142,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R15446856fdcf46ea"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89e8875c685a4be4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6288,61 +6282,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -6394,8 +6388,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6447,8 +6441,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6500,8 +6494,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6553,8 +6547,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6606,8 +6600,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6659,8 +6653,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6712,8 +6706,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str">
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6765,8 +6759,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str">
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6818,8 +6812,8 @@
       </x:c>
       <x:c r="P15" s="9" t="str"/>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str">
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6871,8 +6865,8 @@
       </x:c>
       <x:c r="P16" s="7" t="str"/>
       <x:c r="Q16" s="7" t="str"/>
-      <x:c r="R16" s="21" t="str"/>
-      <x:c r="S16" s="21" t="str">
+      <x:c r="R16" s="7" t="str"/>
+      <x:c r="S16" s="7" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6908,7 +6902,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb6ba0b616cd24523"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc7b606a215cb4e49"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7048,61 +7042,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -7154,8 +7148,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -7205,8 +7199,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -7256,8 +7250,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -7307,8 +7301,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -7358,8 +7352,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -7409,8 +7403,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -7460,8 +7454,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -7511,8 +7505,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -7546,7 +7540,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc7897387e4bf4d90"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda66e97cfc8640b7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7686,61 +7680,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -7786,10 +7780,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>REV-SRC-IWO</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/SSV_Iwo_Jima</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -7825,7 +7819,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf9a4effcaba04c41"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c40fc871c2643a0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7965,61 +7959,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -8065,10 +8059,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>REV-SRC-DAH</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Jill_Dah</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -8114,10 +8108,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>REV-SRC-IWO</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/SSV_Iwo_Jima</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -8153,7 +8147,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra035b3044db94a2a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re44edd345cd64b1b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8293,61 +8287,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -8393,10 +8387,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>REV-SRC-SKARR</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Skarr</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -8432,7 +8426,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R77aa8db3d7044b0a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc829d1c49f96434b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8572,61 +8566,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -8676,8 +8670,8 @@
       <x:c r="O7" s="9" t="str"/>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -8725,8 +8719,8 @@
       <x:c r="O8" s="7" t="str"/>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -8774,8 +8768,8 @@
       <x:c r="O9" s="9" t="str"/>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -8823,8 +8817,8 @@
       <x:c r="O10" s="7" t="str"/>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -8872,8 +8866,8 @@
       <x:c r="O11" s="9" t="str"/>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -8921,8 +8915,8 @@
       <x:c r="O12" s="7" t="str"/>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D12">
@@ -8956,7 +8950,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Redd6ad91c9024575"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc033240389084e15"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9096,61 +9090,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -9196,10 +9190,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>REV-SRC-PUB</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://www.penguinrandomhouse.com/books/89889/mass-effect-revelation-by-drew-karpyshyn/</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -9245,10 +9239,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>REV-SRC-PUB</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://www.penguinrandomhouse.com/books/89889/mass-effect-revelation-by-drew-karpyshyn/</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -9294,10 +9288,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>REV-SRC-DAH</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Jill_Dah</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -9333,7 +9327,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f868c32a64a4787"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1117ecf021f442e1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9473,61 +9467,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -9579,8 +9573,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="82" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -9630,8 +9624,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="82" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -9681,8 +9675,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -9732,8 +9726,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D10">
@@ -9767,7 +9761,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2955720b3b604bdb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3cbd2f37d2334ba3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9907,61 +9901,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -10013,8 +10007,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -10064,8 +10058,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -10115,8 +10109,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -10166,8 +10160,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -10217,8 +10211,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -10268,8 +10262,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -10319,8 +10313,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -10370,8 +10364,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
     <x:row r="15" ht="68" customHeight="1">
       <x:c r="A15" s="18" t="str">
@@ -10421,8 +10415,8 @@
       </x:c>
       <x:c r="P15" s="9" t="str"/>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str"/>
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str"/>
     </x:row>
     <x:row r="16" ht="68" customHeight="1">
       <x:c r="A16" s="19" t="str">
@@ -10472,8 +10466,8 @@
       </x:c>
       <x:c r="P16" s="7" t="str"/>
       <x:c r="Q16" s="7" t="str"/>
-      <x:c r="R16" s="21" t="str"/>
-      <x:c r="S16" s="21" t="str"/>
+      <x:c r="R16" s="7" t="str"/>
+      <x:c r="S16" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D16">
@@ -10507,7 +10501,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5aeaf892edc64d3b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7eaab3a53f1d4231"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10647,61 +10641,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -10753,8 +10747,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -10804,8 +10798,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -10855,8 +10849,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -10906,8 +10900,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -10957,8 +10951,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -11008,8 +11002,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="68" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -11059,8 +11053,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="68" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -11110,8 +11104,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
     <x:row r="15" ht="68" customHeight="1">
       <x:c r="A15" s="18" t="str">
@@ -11161,8 +11155,8 @@
       </x:c>
       <x:c r="P15" s="9" t="str"/>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str"/>
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str"/>
     </x:row>
     <x:row r="16" ht="68" customHeight="1">
       <x:c r="A16" s="19" t="str">
@@ -11212,8 +11206,8 @@
       </x:c>
       <x:c r="P16" s="7" t="str"/>
       <x:c r="Q16" s="7" t="str"/>
-      <x:c r="R16" s="21" t="str"/>
-      <x:c r="S16" s="21" t="str"/>
+      <x:c r="R16" s="7" t="str"/>
+      <x:c r="S16" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D16">
@@ -11247,7 +11241,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb76d5689f324b97"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3e90ef9a875d4777"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11387,61 +11381,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -11493,8 +11487,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -11544,8 +11538,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -11595,8 +11589,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -11646,8 +11640,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D10">
@@ -11681,7 +11675,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1bf22b5fb2da4c32"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07cc04de190c473a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11821,61 +11815,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -11925,8 +11919,8 @@
       <x:c r="O7" s="9" t="str"/>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="82" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -11974,8 +11968,8 @@
       <x:c r="O8" s="7" t="str"/>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -12023,8 +12017,8 @@
       <x:c r="O9" s="9" t="str"/>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -12072,8 +12066,8 @@
       <x:c r="O10" s="7" t="str"/>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -12121,8 +12115,8 @@
       <x:c r="O11" s="9" t="str"/>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D11">
@@ -12156,7 +12150,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfeff307e39294bb9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R22b9f3df85db45ec"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12296,61 +12290,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -12400,8 +12394,8 @@
       <x:c r="O7" s="9" t="str"/>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -12449,8 +12443,8 @@
       <x:c r="O8" s="7" t="str"/>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="44" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -12498,8 +12492,8 @@
       <x:c r="O9" s="9" t="str"/>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="44" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -12547,8 +12541,8 @@
       <x:c r="O10" s="7" t="str"/>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -12596,8 +12590,8 @@
       <x:c r="O11" s="9" t="str"/>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="44" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -12645,8 +12639,8 @@
       <x:c r="O12" s="7" t="str"/>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="44" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -12694,8 +12688,8 @@
       <x:c r="O13" s="9" t="str"/>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="44" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -12743,8 +12737,8 @@
       <x:c r="O14" s="7" t="str"/>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -12778,7 +12772,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6a8255cc0f0a480c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R460bb4d0fc564cba"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12918,61 +12912,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -13024,8 +13018,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -13075,8 +13069,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -13126,8 +13120,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -13177,8 +13171,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -13228,8 +13222,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -13279,8 +13273,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -13330,8 +13324,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -13381,8 +13375,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
     <x:row r="15" ht="68" customHeight="1">
       <x:c r="A15" s="18" t="str">
@@ -13424,8 +13418,8 @@
       <x:c r="O15" s="9" t="str"/>
       <x:c r="P15" s="9" t="str"/>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str"/>
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str"/>
     </x:row>
     <x:row r="16" ht="68" customHeight="1">
       <x:c r="A16" s="19" t="str">
@@ -13467,8 +13461,8 @@
       <x:c r="O16" s="7" t="str"/>
       <x:c r="P16" s="7" t="str"/>
       <x:c r="Q16" s="7" t="str"/>
-      <x:c r="R16" s="21" t="str"/>
-      <x:c r="S16" s="21" t="str"/>
+      <x:c r="R16" s="7" t="str"/>
+      <x:c r="S16" s="7" t="str"/>
     </x:row>
     <x:row r="17" ht="54" customHeight="1">
       <x:c r="A17" s="18" t="str">
@@ -13510,8 +13504,8 @@
       <x:c r="O17" s="9" t="str"/>
       <x:c r="P17" s="9" t="str"/>
       <x:c r="Q17" s="9" t="str"/>
-      <x:c r="R17" s="20" t="str"/>
-      <x:c r="S17" s="20" t="str"/>
+      <x:c r="R17" s="9" t="str"/>
+      <x:c r="S17" s="9" t="str"/>
     </x:row>
     <x:row r="18" ht="54" customHeight="1">
       <x:c r="A18" s="19" t="str">
@@ -13553,8 +13547,8 @@
       <x:c r="O18" s="7" t="str"/>
       <x:c r="P18" s="7" t="str"/>
       <x:c r="Q18" s="7" t="str"/>
-      <x:c r="R18" s="21" t="str"/>
-      <x:c r="S18" s="21" t="str"/>
+      <x:c r="R18" s="7" t="str"/>
+      <x:c r="S18" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D18">
@@ -13588,7 +13582,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b7b021707094a00"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4cfc1bc2df9a4d5e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13728,61 +13722,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -13828,10 +13822,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>REV-SRC-SKARR</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Skarr</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -13877,10 +13871,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>REV-SRC-WIKI</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect:_Revelation</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -13924,8 +13918,8 @@
         <x:v>Limite de continuité / contrôle transversal</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -13969,8 +13963,8 @@
         <x:v>Limite de continuité / contrôle transversal</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -14016,10 +14010,10 @@
       <x:c r="Q11" s="9" t="str">
         <x:v>REV-SRC-IWO</x:v>
       </x:c>
-      <x:c r="R11" s="20" t="str">
+      <x:c r="R11" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/SSV_Iwo_Jima</x:v>
       </x:c>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="S11" s="9" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -14063,8 +14057,8 @@
         <x:v>Limite de continuité / contrôle transversal</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -14108,8 +14102,8 @@
         <x:v>Limite de continuité / contrôle transversal</x:v>
       </x:c>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str">
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -14145,7 +14139,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc50849d9818a4c47"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra6b9f2a5f0cf444a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14210,10 +14204,10 @@
       <x:c r="F5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Champ</x:v>
       </x:c>
-      <x:c r="B6" s="32" t="str">
+      <x:c r="B6" s="30" t="str">
         <x:v>Définition</x:v>
       </x:c>
       <x:c r="C6" s="2"/>
@@ -14262,7 +14256,7 @@
         <x:v>Projet</x:v>
       </x:c>
       <x:c r="B10" s="7" t="str">
-        <x:v>Anderson, Kahlee, Saren et la crise de Sidon ; relations entre Alliance, Spectres et mercenaires ; propositions de niveaux d’enquête et de sauvetage.</x:v>
+        <x:v>158 fiches de production ; 6 fiches au stade Prototype de portée partielle. Les autres livrables restent des spécifications ; aucun achèvement intégral 1:1 revendiqué.</x:v>
       </x:c>
       <x:c r="C10" s="2"/>
       <x:c r="D10" s="2"/>
@@ -14281,11 +14275,11 @@
       <x:c r="E11" s="2"/>
       <x:c r="F11" s="2"/>
     </x:row>
-    <x:row r="12" ht="40" customHeight="1">
+    <x:row r="12" ht="30" customHeight="1">
       <x:c r="A12" s="7" t="str">
         <x:v>Date de référence</x:v>
       </x:c>
-      <x:c r="B12" s="44" t="d">
+      <x:c r="B12" s="42" t="d">
         <x:v>2026-10-22T12:00:00.000Z</x:v>
       </x:c>
       <x:c r="C12" s="2"/>
@@ -14438,22 +14432,22 @@
       <x:c r="F25" s="2"/>
     </x:row>
     <x:row r="26" ht="34" customHeight="1">
-      <x:c r="A26" s="30" t="str">
+      <x:c r="A26" s="28" t="str">
         <x:v>Source</x:v>
       </x:c>
-      <x:c r="B26" s="31" t="str">
+      <x:c r="B26" s="29" t="str">
         <x:v>Titre</x:v>
       </x:c>
-      <x:c r="C26" s="31" t="str">
+      <x:c r="C26" s="29" t="str">
         <x:v>Type</x:v>
       </x:c>
-      <x:c r="D26" s="31" t="str">
+      <x:c r="D26" s="29" t="str">
         <x:v>URL</x:v>
       </x:c>
-      <x:c r="E26" s="31" t="str">
+      <x:c r="E26" s="29" t="str">
         <x:v>Périmètre</x:v>
       </x:c>
-      <x:c r="F26" s="32" t="str">
+      <x:c r="F26" s="30" t="str">
         <x:v>Accès et limites</x:v>
       </x:c>
     </x:row>
@@ -14662,13 +14656,13 @@
       <x:c r="F38" s="2"/>
     </x:row>
     <x:row r="39" ht="34" customHeight="1">
-      <x:c r="A39" s="30" t="str">
+      <x:c r="A39" s="28" t="str">
         <x:v>Domaine</x:v>
       </x:c>
-      <x:c r="B39" s="31" t="str">
+      <x:c r="B39" s="29" t="str">
         <x:v>Couverture actuelle</x:v>
       </x:c>
-      <x:c r="C39" s="32" t="str">
+      <x:c r="C39" s="30" t="str">
         <x:v>Travail restant</x:v>
       </x:c>
       <x:c r="D39" s="2"/>
@@ -14745,10 +14739,16 @@
       <x:c r="E44" s="2"/>
       <x:c r="F44" s="2"/>
     </x:row>
-    <x:row r="45" ht="22" customHeight="1">
-      <x:c r="A45" s="2"/>
-      <x:c r="B45" s="2"/>
-      <x:c r="C45" s="2"/>
+    <x:row r="45" ht="96" customHeight="1">
+      <x:c r="A45" s="6" t="str">
+        <x:v>Complément pouvoirs, modules et lectures</x:v>
+      </x:c>
+      <x:c r="B45" s="6" t="str">
+        <x:v>0 fiches de pouvoirs utilisées, 0 familles de modules préparables et 6 références consultables dans une lecture documentaire. Les chemins et preuves sont inscrits sur les seules lignes Prototype.</x:v>
+      </x:c>
+      <x:c r="C45" s="6" t="str">
+        <x:v>Arbres et progression complets, modèles et rangs exacts, campagnes et dialogues intégraux, niveaux et ressources visuelles propres à l’œuvre restent à réaliser ou vérifier. Les références lues ne rendent pas leurs personnages jouables.</x:v>
+      </x:c>
       <x:c r="D45" s="2"/>
       <x:c r="E45" s="2"/>
       <x:c r="F45" s="2"/>
@@ -15304,6 +15304,14 @@
       <x:c r="D114" s="2"/>
       <x:c r="E114" s="2"/>
       <x:c r="F114" s="2"/>
+    </x:row>
+    <x:row r="115" ht="22" customHeight="1">
+      <x:c r="A115" s="2"/>
+      <x:c r="B115" s="2"/>
+      <x:c r="C115" s="2"/>
+      <x:c r="D115" s="2"/>
+      <x:c r="E115" s="2"/>
+      <x:c r="F115" s="2"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15445,61 +15453,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -15545,10 +15553,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>REV-SRC-WIKI</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect:_Revelation</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -15594,10 +15602,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>REV-SRC-SKARR</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Skarr</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -15643,10 +15651,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>REV-SRC-SKARR</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Skarr</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -15692,10 +15700,10 @@
       <x:c r="Q10" s="7" t="str">
         <x:v>REV-SRC-SKARR</x:v>
       </x:c>
-      <x:c r="R10" s="21" t="str">
+      <x:c r="R10" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Skarr</x:v>
       </x:c>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="S10" s="7" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -15741,10 +15749,10 @@
       <x:c r="Q11" s="9" t="str">
         <x:v>REV-SRC-JELLA</x:v>
       </x:c>
-      <x:c r="R11" s="20" t="str">
+      <x:c r="R11" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Jella</x:v>
       </x:c>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="S11" s="9" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -15790,10 +15798,10 @@
       <x:c r="Q12" s="7" t="str">
         <x:v>REV-SRC-AND</x:v>
       </x:c>
-      <x:c r="R12" s="21" t="str">
+      <x:c r="R12" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/David_Anderson</x:v>
       </x:c>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="S12" s="7" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -15839,10 +15847,10 @@
       <x:c r="Q13" s="9" t="str">
         <x:v>REV-SRC-SAREN</x:v>
       </x:c>
-      <x:c r="R13" s="20" t="str">
+      <x:c r="R13" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Saren_Arterius</x:v>
       </x:c>
-      <x:c r="S13" s="20" t="str">
+      <x:c r="S13" s="9" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -15878,7 +15886,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra350bac2b2254eb5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ef5039969f94cc7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15905,7 +15913,7 @@
     <x:col min="16" max="16" width="45" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="24" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="81" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="73" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="255" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22" customHeight="1">
@@ -16018,65 +16026,65 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="68" customHeight="1">
+    <x:row r="7" ht="82" customHeight="1">
       <x:c r="A7" s="18" t="str">
         <x:v>REV-REF-SUNS</x:v>
       </x:c>
@@ -16084,7 +16092,7 @@
         <x:v>Soleils Bleus</x:v>
       </x:c>
       <x:c r="C7" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D7" s="16" t="str">
         <x:v>Établi</x:v>
@@ -16103,7 +16111,7 @@
       <x:c r="J7" s="9" t="str"/>
       <x:c r="K7" s="9" t="str"/>
       <x:c r="L7" s="9" t="str">
-        <x:v>Codex ref.rev.suns ; affichage bref avec source.</x:v>
+        <x:v>Référence documentaire REV-REF-SUNS consultable dans les lectures de src/chronicle-story.js, avec sources et progression séparée. Aucune scène, carte, animation ou incarnation de personnage n’est produite par cette fiche.</x:v>
       </x:c>
       <x:c r="M7" s="9" t="str">
         <x:v>Conserver la trajectoire menant à Mass Effect : Anderson ne devient pas Spectre dans ce module et les intentions de Saren ne deviennent pas un savoir public anticipé.</x:v>
@@ -16118,14 +16126,14 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>REV-SRC-BLUE</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Blue_Suns</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
-        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="68" customHeight="1">
+      <x:c r="S7" s="9" t="str">
+        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène. Prototype limité à une paraphrase documentaire sourcée et aux références visitées. Les autres livrables de l’œuvre restent à produire ; les personnages mentionnés ne sont pas recrutables et les lieux cités ne deviennent pas des niveaux.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="82" customHeight="1">
       <x:c r="A8" s="19" t="str">
         <x:v>REV-REF-ALLIANCE</x:v>
       </x:c>
@@ -16133,7 +16141,7 @@
         <x:v>Alliance interstellaire</x:v>
       </x:c>
       <x:c r="C8" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D8" s="17" t="str">
         <x:v>Établi</x:v>
@@ -16152,7 +16160,7 @@
       <x:c r="J8" s="7" t="str"/>
       <x:c r="K8" s="7" t="str"/>
       <x:c r="L8" s="7" t="str">
-        <x:v>Codex ref.rev.alliance ; affichage bref avec source.</x:v>
+        <x:v>Référence documentaire REV-REF-ALLIANCE consultable dans les lectures de src/chronicle-story.js, avec sources et progression séparée. Aucune scène, carte, animation ou incarnation de personnage n’est produite par cette fiche.</x:v>
       </x:c>
       <x:c r="M8" s="7" t="str">
         <x:v>Conserver la trajectoire menant à Mass Effect : Anderson ne devient pas Spectre dans ce module et les intentions de Saren ne deviennent pas un savoir public anticipé.</x:v>
@@ -16167,14 +16175,14 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>REV-SRC-PUB</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://www.penguinrandomhouse.com/books/89889/mass-effect-revelation-by-drew-karpyshyn/</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
-        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="68" customHeight="1">
+      <x:c r="S8" s="7" t="str">
+        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène. Prototype limité à une paraphrase documentaire sourcée et aux références visitées. Les autres livrables de l’œuvre restent à produire ; les personnages mentionnés ne sont pas recrutables et les lieux cités ne deviennent pas des niveaux.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="82" customHeight="1">
       <x:c r="A9" s="18" t="str">
         <x:v>REV-REF-AI</x:v>
       </x:c>
@@ -16182,7 +16190,7 @@
         <x:v>Recherche en intelligence artificielle</x:v>
       </x:c>
       <x:c r="C9" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D9" s="16" t="str">
         <x:v>Établi</x:v>
@@ -16201,7 +16209,7 @@
       <x:c r="J9" s="9" t="str"/>
       <x:c r="K9" s="9" t="str"/>
       <x:c r="L9" s="9" t="str">
-        <x:v>Codex ref.rev.ai ; affichage bref avec source.</x:v>
+        <x:v>Référence documentaire REV-REF-AI consultable dans les lectures de src/chronicle-story.js, avec sources et progression séparée. Aucune scène, carte, animation ou incarnation de personnage n’est produite par cette fiche.</x:v>
       </x:c>
       <x:c r="M9" s="9" t="str">
         <x:v>Conserver la trajectoire menant à Mass Effect : Anderson ne devient pas Spectre dans ce module et les intentions de Saren ne deviennent pas un savoir public anticipé.</x:v>
@@ -16216,11 +16224,11 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>REV-SRC-WIKI</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect:_Revelation</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
-        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
+      <x:c r="S9" s="9" t="str">
+        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène. Prototype limité à une paraphrase documentaire sourcée et aux références visitées. Les autres livrables de l’œuvre restent à produire ; les personnages mentionnés ne sont pas recrutables et les lieux cités ne deviennent pas des niveaux.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -16255,7 +16263,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R97592243b8fe453a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc96b6d353ad84798"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16282,7 +16290,7 @@
     <x:col min="16" max="16" width="45" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="24" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="69" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="73" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="255" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22" customHeight="1">
@@ -16395,65 +16403,65 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="68" customHeight="1">
+    <x:row r="7" ht="82" customHeight="1">
       <x:c r="A7" s="18" t="str">
         <x:v>REV-REF-SIDON</x:v>
       </x:c>
@@ -16461,7 +16469,7 @@
         <x:v>Sidon</x:v>
       </x:c>
       <x:c r="C7" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D7" s="16" t="str">
         <x:v>Établi</x:v>
@@ -16480,7 +16488,7 @@
       <x:c r="J7" s="9" t="str"/>
       <x:c r="K7" s="9" t="str"/>
       <x:c r="L7" s="9" t="str">
-        <x:v>Codex ref.rev.sidon ; affichage bref avec source.</x:v>
+        <x:v>Référence documentaire REV-REF-SIDON consultable dans les lectures de src/chronicle-story.js, avec sources et progression séparée. Aucune scène, carte, animation ou incarnation de personnage n’est produite par cette fiche.</x:v>
       </x:c>
       <x:c r="M7" s="9" t="str">
         <x:v>Conserver la trajectoire menant à Mass Effect : Anderson ne devient pas Spectre dans ce module et les intentions de Saren ne deviennent pas un savoir public anticipé.</x:v>
@@ -16495,14 +16503,14 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>REV-SRC-WIKI</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect:_Revelation</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
-        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="68" customHeight="1">
+      <x:c r="S7" s="9" t="str">
+        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène. Prototype limité à une paraphrase documentaire sourcée et aux références visitées. Les autres livrables de l’œuvre restent à produire ; les personnages mentionnés ne sont pas recrutables et les lieux cités ne deviennent pas des niveaux.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="82" customHeight="1">
       <x:c r="A8" s="19" t="str">
         <x:v>REV-REF-ELYSIUM</x:v>
       </x:c>
@@ -16510,7 +16518,7 @@
         <x:v>Elysium</x:v>
       </x:c>
       <x:c r="C8" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D8" s="17" t="str">
         <x:v>Établi</x:v>
@@ -16529,7 +16537,7 @@
       <x:c r="J8" s="7" t="str"/>
       <x:c r="K8" s="7" t="str"/>
       <x:c r="L8" s="7" t="str">
-        <x:v>Codex ref.rev.elysium ; affichage bref avec source.</x:v>
+        <x:v>Référence documentaire REV-REF-ELYSIUM consultable dans les lectures de src/chronicle-story.js, avec sources et progression séparée. Aucune scène, carte, animation ou incarnation de personnage n’est produite par cette fiche.</x:v>
       </x:c>
       <x:c r="M8" s="7" t="str">
         <x:v>Conserver la trajectoire menant à Mass Effect : Anderson ne devient pas Spectre dans ce module et les intentions de Saren ne deviennent pas un savoir public anticipé.</x:v>
@@ -16544,14 +16552,14 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>REV-SRC-SKARR</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Skarr</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
-        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="68" customHeight="1">
+      <x:c r="S8" s="7" t="str">
+        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène. Prototype limité à une paraphrase documentaire sourcée et aux références visitées. Les autres livrables de l’œuvre restent à produire ; les personnages mentionnés ne sont pas recrutables et les lieux cités ne deviennent pas des niveaux.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="82" customHeight="1">
       <x:c r="A9" s="18" t="str">
         <x:v>REV-REF-CAMALA</x:v>
       </x:c>
@@ -16559,7 +16567,7 @@
         <x:v>Camala</x:v>
       </x:c>
       <x:c r="C9" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D9" s="16" t="str">
         <x:v>Établi</x:v>
@@ -16578,7 +16586,7 @@
       <x:c r="J9" s="9" t="str"/>
       <x:c r="K9" s="9" t="str"/>
       <x:c r="L9" s="9" t="str">
-        <x:v>Codex ref.rev.camala ; affichage bref avec source.</x:v>
+        <x:v>Référence documentaire REV-REF-CAMALA consultable dans les lectures de src/chronicle-story.js, avec sources et progression séparée. Aucune scène, carte, animation ou incarnation de personnage n’est produite par cette fiche.</x:v>
       </x:c>
       <x:c r="M9" s="9" t="str">
         <x:v>Conserver la trajectoire menant à Mass Effect : Anderson ne devient pas Spectre dans ce module et les intentions de Saren ne deviennent pas un savoir public anticipé.</x:v>
@@ -16593,11 +16601,11 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>REV-SRC-SKARR</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Skarr</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
-        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
+      <x:c r="S9" s="9" t="str">
+        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène. Prototype limité à une paraphrase documentaire sourcée et aux références visitées. Les autres livrables de l’œuvre restent à produire ; les personnages mentionnés ne sont pas recrutables et les lieux cités ne deviennent pas des niveaux.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
@@ -16642,10 +16650,10 @@
       <x:c r="Q10" s="7" t="str">
         <x:v>REV-SRC-WIKI</x:v>
       </x:c>
-      <x:c r="R10" s="21" t="str">
+      <x:c r="R10" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect:_Revelation</x:v>
       </x:c>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="S10" s="7" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -16681,7 +16689,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R487cba1f2158424c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9aff43667d404470"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16821,61 +16829,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -16925,8 +16933,8 @@
       <x:c r="O7" s="9" t="str"/>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -16976,8 +16984,8 @@
       <x:c r="O8" s="7" t="str"/>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -17027,8 +17035,8 @@
       <x:c r="O9" s="9" t="str"/>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -17078,8 +17086,8 @@
       <x:c r="O10" s="7" t="str"/>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -17129,8 +17137,8 @@
       <x:c r="O11" s="9" t="str"/>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -17180,8 +17188,8 @@
       <x:c r="O12" s="7" t="str"/>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -17231,8 +17239,8 @@
       <x:c r="O13" s="9" t="str"/>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str">
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -17282,8 +17290,8 @@
       <x:c r="O14" s="7" t="str"/>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str">
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -17319,7 +17327,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7e7ded5f01d147e4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra709be759a0746ac"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17459,61 +17467,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -17565,8 +17573,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -17618,8 +17626,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -17671,8 +17679,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -17724,8 +17732,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -17777,8 +17785,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -17830,8 +17838,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -17883,8 +17891,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str">
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -17936,8 +17944,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str">
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -17973,7 +17981,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f08f471199945c9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc61de01214f4781"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18113,61 +18121,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -18219,8 +18227,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -18270,8 +18278,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -18321,8 +18329,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -18372,8 +18380,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -18423,8 +18431,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -18474,8 +18482,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -18525,8 +18533,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -18576,8 +18584,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -18611,7 +18619,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8cd15248942f4c43"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R039c4e154c564b59"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18751,61 +18759,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -18851,10 +18859,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>REV-SRC-SKARR</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Skarr</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -18890,7 +18898,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re04baf89ecf245f4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd21c9d2f8a85469d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Revelation_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Revelation_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rbadfbf77a83943eb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="Rd5121f97b7a84763"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R27bf38292c0c463a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R977e0bc9020d40ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R41028a70b71349f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R180a60fe720f425d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R7276565e08c94737"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R38873c10765e4ae4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R19f62fb58f7d4a95"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R49f60ec43bbb4fda"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R3d5a9165ee8a40ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R39bce930b1bb436c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R18f8e5f2ecbc40f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="Rad11ce2c56fb47cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R94451aecdf1144df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R1930d91796a44962"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R418f12c803ac47d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="Re1a817d956964f73"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R7031cc52b2fe4fc8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="Re42b3561b0184911"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R0b3319192583403d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R59d78e450dfa4531"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R424b76f9f0fe421c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R6fc0ed0d59a8434a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R9c2c05c7f7114fe2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R055d01008ebf4792"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R2808e5ffe5e44dda"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="Rc21d5227470e4314"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rc919d95be6684001"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="Rd4b6fc0f96e04dcf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R2007584257e543b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R7bebf512876a4eb9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="Rfc63994ec32d4078"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R428d7fea7ed04828"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="Recfad696547747d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="Rb54e4fcfa0124411"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Rdbe88deecaff4269"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R31aa971c2e464a71"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="Rb07abfe8068c4218"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="Rbd73f79a3cc44f36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R1223062885234757"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R2bbacc1aa14c4d4e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="Rc091b928da074742"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R7aadf4a83926423f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="Rc4b5fd3d02234f5f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R35896d2b1389408e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="Rda95faec830c4730"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="Rcce7ebdc9027473a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="Rcc8f34daab4c4c9c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="Rbc067709837247c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="Rb6861bae4bf644da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R59a29d48cc9b4bbc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="Rd3e2710d1def41b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R84027e7b26aa4c84"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R338bf48b916248cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R1e09f83a8a3344e8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4228,7 +4228,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R22dfc1a385e249b2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3a927456d104e76"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4866,7 +4866,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R84ef90daef3847b1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd4af28b18d8d4323"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5504,7 +5504,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d923c4831ac47fd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd8a221fed3d84725"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6142,7 +6142,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89e8875c685a4be4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d26b154f3b84906"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6902,7 +6902,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc7b606a215cb4e49"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R997ac3cf1ad2431e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7540,7 +7540,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda66e97cfc8640b7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde7835cf8d074264"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7819,7 +7819,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c40fc871c2643a0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9b9ccc171b0c4644"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8147,7 +8147,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re44edd345cd64b1b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1bdff269bcb04bdd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8426,7 +8426,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc829d1c49f96434b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R41dfce18382b44aa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8950,7 +8950,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc033240389084e15"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc55ba5efcc7644a2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9327,7 +9327,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1117ecf021f442e1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R049a6d202c724869"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9761,7 +9761,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3cbd2f37d2334ba3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6552b02010fb4ae3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10501,7 +10501,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7eaab3a53f1d4231"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06df4162b8c0451f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11241,7 +11241,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3e90ef9a875d4777"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2955e991605649dc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11675,7 +11675,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07cc04de190c473a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2ced2ac30202440e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12150,7 +12150,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R22b9f3df85db45ec"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd1732c6f600440ed"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12772,7 +12772,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R460bb4d0fc564cba"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdceaf5ce1d51467f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13582,7 +13582,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4cfc1bc2df9a4d5e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e38c19f38b549b1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14139,7 +14139,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra6b9f2a5f0cf444a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d7ec1162ba24d6f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15886,7 +15886,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ef5039969f94cc7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9eda9143c1c44bb8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16263,7 +16263,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc96b6d353ad84798"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc93fd513e06d4809"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16689,7 +16689,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9aff43667d404470"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf6d9341a149c47f9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17327,7 +17327,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra709be759a0746ac"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R32565541cd3f473a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17981,7 +17981,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc61de01214f4781"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ee2365f2f0f43d5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18619,7 +18619,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R039c4e154c564b59"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R35dcf02f03504a0d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18898,7 +18898,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd21c9d2f8a85469d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb2a1164e99b34ec3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Revelation_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Revelation_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rc919d95be6684001"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="Rd4b6fc0f96e04dcf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R2007584257e543b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R7bebf512876a4eb9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="Rfc63994ec32d4078"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R428d7fea7ed04828"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="Recfad696547747d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="Rb54e4fcfa0124411"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Rdbe88deecaff4269"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R31aa971c2e464a71"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="Rb07abfe8068c4218"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="Rbd73f79a3cc44f36"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R1223062885234757"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R2bbacc1aa14c4d4e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="Rc091b928da074742"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R7aadf4a83926423f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="Rc4b5fd3d02234f5f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R35896d2b1389408e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="Rda95faec830c4730"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="Rcce7ebdc9027473a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="Rcc8f34daab4c4c9c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="Rbc067709837247c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="Rb6861bae4bf644da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R59a29d48cc9b4bbc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="Rd3e2710d1def41b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R84027e7b26aa4c84"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R338bf48b916248cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R1e09f83a8a3344e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R8f3b01f5e0bd4156"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R2084328145a44f5f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R73393806fd074369"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R8d7ed8ded306443b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R325e8a4f8a7849fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R9b7a68b997904af8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="Rbc8fee4ec502432f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="Rab800434ef4a471d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Ra13eed6a093543b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="Rfc0612668fd34b13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R6a2b98a763da4b75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="Rd19d7e9cb29a4779"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R28b9a5772f1c4d83"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R58bd8289ddda41b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R3d6e40ed700d404e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R8dd829c1b16d4ec2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R62ed580a00a64f51"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="Rc85a6d8344924e39"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R411e493387eb430c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R20d8fa7c7f294346"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R66cf4c17978542f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R5b5e09b87c9a4d19"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R310935443fdc4a2f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="Rb0b18d0a79754204"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R4ebc55fb4c344911"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="Rd281979b36dc407d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R3e4545c2c5d644e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R244546a7f9cb4064"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4228,7 +4228,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3a927456d104e76"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3083e722482e43b0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4866,7 +4866,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd4af28b18d8d4323"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5572d3a397564dfa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5504,7 +5504,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd8a221fed3d84725"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R76f6e451b2404fca"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6142,7 +6142,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d26b154f3b84906"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ecc0e986fb6453b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6902,7 +6902,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R997ac3cf1ad2431e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R950bf681db8f48c4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7540,7 +7540,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde7835cf8d074264"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re25f4c566cf04453"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7819,7 +7819,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9b9ccc171b0c4644"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6e8f01a1824243d6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8147,7 +8147,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1bdff269bcb04bdd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8731980db1f44dac"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8426,7 +8426,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R41dfce18382b44aa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R05e7ac1caa70441e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8950,7 +8950,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc55ba5efcc7644a2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3a93f6fee6b4df4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9327,7 +9327,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R049a6d202c724869"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6da079634196403e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9761,7 +9761,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6552b02010fb4ae3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1d2d1bc703414dd4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10501,7 +10501,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06df4162b8c0451f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f165e2599d349bc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11241,7 +11241,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2955e991605649dc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb61ceb8934ad4952"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11675,7 +11675,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2ced2ac30202440e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf8eccc1312ed4d11"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12150,7 +12150,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd1732c6f600440ed"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2a4c1f5e8aa74885"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12772,7 +12772,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdceaf5ce1d51467f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c6f713b4f764b0a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13582,7 +13582,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e38c19f38b549b1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd28587f4e90642a5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14139,7 +14139,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d7ec1162ba24d6f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rccd43b46e786460a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15886,7 +15886,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9eda9143c1c44bb8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R01d4dcbc82d640f2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16263,7 +16263,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc93fd513e06d4809"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd0c153b39e684d64"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16689,7 +16689,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf6d9341a149c47f9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re4d2a32f1bf54eeb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17327,7 +17327,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R32565541cd3f473a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdda04e9f705f4adf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17981,7 +17981,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ee2365f2f0f43d5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85be869c7ae14324"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18619,7 +18619,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R35dcf02f03504a0d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0de3219c22964937"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18898,7 +18898,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb2a1164e99b34ec3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R86175f42d2d9452d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Revelation_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Revelation_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R8f3b01f5e0bd4156"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R2084328145a44f5f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R73393806fd074369"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R8d7ed8ded306443b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R325e8a4f8a7849fa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R9b7a68b997904af8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="Rbc8fee4ec502432f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="Rab800434ef4a471d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Ra13eed6a093543b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="Rfc0612668fd34b13"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R6a2b98a763da4b75"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="Rd19d7e9cb29a4779"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R28b9a5772f1c4d83"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R58bd8289ddda41b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R3d6e40ed700d404e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R8dd829c1b16d4ec2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R62ed580a00a64f51"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="Rc85a6d8344924e39"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R411e493387eb430c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R20d8fa7c7f294346"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R66cf4c17978542f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R5b5e09b87c9a4d19"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R310935443fdc4a2f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="Rb0b18d0a79754204"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R4ebc55fb4c344911"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="Rd281979b36dc407d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R3e4545c2c5d644e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R244546a7f9cb4064"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R14a733a67c694ed4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R642ea45af4d84871"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Rc9435422c53d4138"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="Rc7d996da54344cb2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="Reb62dbfcba8e41df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R7a1d2cc3474e4b25"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R4702b26e1e854bc7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R1923f8b685e14a58"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R5b4cdda0573945e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R967b82a6b7d94016"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R7ff3532fe7244024"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="Re2e296ae93744ba3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R175ecd80cd5b49ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R3c48b35ee54943d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R13a003f48a184816"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R68fb189850034c48"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R8f8852a57d554ee9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R77e877e968004692"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R7d25e6dcaab04583"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="Rdb068100fe354a14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R233bdb040c7a4aa0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R14a229c97c0d41b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="Rea221a30cb154743"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="Raeff5af65d0345d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R00d81cebd8d84157"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="Rb7243fe2b406465e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R3a6c611e8063428c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R8e67d6a487284600"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4228,7 +4228,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3083e722482e43b0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc5cfbb7fe8fa42aa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4866,7 +4866,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5572d3a397564dfa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R01ce598dbb884b80"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5504,7 +5504,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R76f6e451b2404fca"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6338a72142e44cdc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6142,7 +6142,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ecc0e986fb6453b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca7e62ff13b24a10"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6902,7 +6902,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R950bf681db8f48c4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R91fa9d5ffc874af1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7540,7 +7540,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re25f4c566cf04453"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R99a57e391c384006"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7819,7 +7819,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6e8f01a1824243d6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb6943691514846fe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8147,7 +8147,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8731980db1f44dac"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfbd63e30ca494f30"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8426,7 +8426,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R05e7ac1caa70441e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbd2b44fa8110470f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8950,7 +8950,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3a93f6fee6b4df4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R97e9e77a64544d7d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9327,7 +9327,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6da079634196403e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re429874d74094d83"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9761,7 +9761,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1d2d1bc703414dd4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf61aa57fe04e4bb4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10501,7 +10501,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f165e2599d349bc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R488c203dd5384f20"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11241,7 +11241,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb61ceb8934ad4952"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R48231236320e4247"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11675,7 +11675,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf8eccc1312ed4d11"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9a9accbeb3614afc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12150,7 +12150,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2a4c1f5e8aa74885"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R08d0a33dc7dd4535"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12772,7 +12772,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c6f713b4f764b0a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a6d817e2f8b494c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13582,7 +13582,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd28587f4e90642a5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R32c7f553c78e4bbc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14139,7 +14139,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rccd43b46e786460a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a65d534effd4e90"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15886,7 +15886,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R01d4dcbc82d640f2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1ce782925328486c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16263,7 +16263,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd0c153b39e684d64"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R240aec2ecf734f90"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16689,7 +16689,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re4d2a32f1bf54eeb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc0e9de39741e4939"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17327,7 +17327,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdda04e9f705f4adf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R63fa9e8a73424958"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17981,7 +17981,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85be869c7ae14324"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7cbe2d31b3f44394"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18619,7 +18619,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0de3219c22964937"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc421204741a0469f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18898,7 +18898,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R86175f42d2d9452d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd85b7c5ad38f46d4"/>
   </x:tableParts>
 </x:worksheet>
 </file>